--- a/DataVaryingTemperature/LSR_20251119_all_materials.xlsx
+++ b/DataVaryingTemperature/LSR_20251119_all_materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deidum\METALS\Results\20251118_delivery_to_WI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0FE14E0-57D4-4C12-BB5D-00EF0F72F1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E927CEA-6288-47CD-BB79-9833F4DCF5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
   <si>
     <t>Attribute</t>
   </si>
@@ -181,15 +181,6 @@
   </si>
   <si>
     <t>Fatigue_Limit</t>
-  </si>
-  <si>
-    <t>Granta Selector</t>
-  </si>
-  <si>
-    <t>Inverse Analysis</t>
-  </si>
-  <si>
-    <t>Calculated</t>
   </si>
 </sst>
 </file>
@@ -613,24 +604,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V18"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="11.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="10.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="11.6640625" style="1" customWidth="1"/>
+    <col min="11" max="14" width="10.44140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" style="1" customWidth="1"/>
-    <col min="18" max="705" width="20.5703125" style="1" customWidth="1"/>
-    <col min="706" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="13.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" style="1" customWidth="1"/>
+    <col min="18" max="704" width="20.5546875" style="1" customWidth="1"/>
+    <col min="705" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="6" t="s">
         <v>4</v>
@@ -684,7 +675,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -738,7 +729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
@@ -751,23 +742,27 @@
       <c r="D3" s="17">
         <v>31660210473.422401</v>
       </c>
-      <c r="E3" s="17">
-        <v>73276522231.125107</v>
-      </c>
-      <c r="F3" s="17">
-        <v>42098834999.111099</v>
-      </c>
-      <c r="G3" s="17">
+      <c r="E3" s="12">
+        <f>D3*EXP(-2000/Q3)</f>
+        <v>318975670.52076489</v>
+      </c>
+      <c r="F3" s="12">
+        <f>0.1*D3*EXP(-3000/Q3)</f>
+        <v>3201691.1808246872</v>
+      </c>
+      <c r="G3" s="12">
         <v>1.0001904096107801</v>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="12">
         <v>168216570.304768</v>
       </c>
-      <c r="I3" s="17">
-        <v>1626009334.9888</v>
-      </c>
-      <c r="J3" s="17">
-        <v>1362827.91216376</v>
+      <c r="I3" s="12">
+        <f>0.1*H3*EXP(-2000/Q3)</f>
+        <v>169477.68982998349</v>
+      </c>
+      <c r="J3" s="12">
+        <f>0.1*H3*EXP(-3000/Q3)</f>
+        <v>17011.179065454031</v>
       </c>
       <c r="K3" s="17">
         <v>1.0002813979562399</v>
@@ -787,14 +782,14 @@
       <c r="P3" s="15">
         <v>0.25</v>
       </c>
-      <c r="Q3" s="7">
-        <v>150</v>
+      <c r="Q3" s="12">
+        <v>435</v>
       </c>
       <c r="R3" s="8">
         <v>112000000</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
@@ -808,10 +803,12 @@
         <v>88122361302.941193</v>
       </c>
       <c r="E4" s="12">
-        <v>43160916887.095703</v>
+        <f t="shared" ref="E4:E5" si="0">D4*EXP(-2000/Q4)</f>
+        <v>425450353.708947</v>
       </c>
       <c r="F4" s="12">
-        <v>2048198742574.49</v>
+        <f t="shared" ref="F4:F5" si="1">0.1*D4*EXP(-3000/Q4)</f>
+        <v>2956175.8899659268</v>
       </c>
       <c r="G4" s="12">
         <v>0.99968676964325098</v>
@@ -820,10 +817,12 @@
         <v>331895501.95574099</v>
       </c>
       <c r="I4" s="12">
-        <v>411398268.51887101</v>
+        <f t="shared" ref="I4:I5" si="2">0.1*H4*EXP(-2000/Q4)</f>
+        <v>160237.4886619903</v>
       </c>
       <c r="J4" s="12">
-        <v>211126489.35119501</v>
+        <f t="shared" ref="J4:J5" si="3">0.1*H4*EXP(-3000/Q4)</f>
+        <v>11133.853727509615</v>
       </c>
       <c r="K4" s="12">
         <v>1.00011111067342</v>
@@ -843,14 +842,14 @@
       <c r="P4" s="15">
         <v>0.74</v>
       </c>
-      <c r="Q4" s="7">
-        <v>150</v>
+      <c r="Q4" s="12">
+        <v>375</v>
       </c>
       <c r="R4" s="8">
         <v>118000000</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -864,10 +863,12 @@
         <v>92976880986.810806</v>
       </c>
       <c r="E5" s="12">
-        <v>36504792717.403801</v>
+        <f t="shared" si="0"/>
+        <v>306684777.10425931</v>
       </c>
       <c r="F5" s="12">
-        <v>2472842900671.1802</v>
+        <f t="shared" si="1"/>
+        <v>1761371.0038603023</v>
       </c>
       <c r="G5" s="12">
         <v>0.99992423656867901</v>
@@ -876,10 +877,12 @@
         <v>413532439.30818099</v>
       </c>
       <c r="I5" s="12">
-        <v>478670621.39346302</v>
+        <f t="shared" si="2"/>
+        <v>136403.9131325568</v>
       </c>
       <c r="J5" s="12">
-        <v>10759114.630594</v>
+        <f t="shared" si="3"/>
+        <v>7834.0340095552874</v>
       </c>
       <c r="K5" s="12">
         <v>1.0004243155682</v>
@@ -899,14 +902,14 @@
       <c r="P5" s="15">
         <v>0.15</v>
       </c>
-      <c r="Q5" s="7">
-        <v>200</v>
+      <c r="Q5" s="12">
+        <v>350</v>
       </c>
       <c r="R5" s="8">
         <v>150000000</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
@@ -955,16 +958,16 @@
       <c r="P6" s="15">
         <v>0.46</v>
       </c>
-      <c r="Q6" s="7">
-        <v>400</v>
+      <c r="Q6" s="12">
+        <v>1050</v>
       </c>
       <c r="R6" s="8">
         <v>229000000</v>
       </c>
-      <c r="U6" s="5"/>
-      <c r="W6" s="5"/>
-    </row>
-    <row r="7" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="T6" s="5"/>
+      <c r="V6" s="5"/>
+    </row>
+    <row r="7" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -1013,14 +1016,14 @@
       <c r="P7" s="15">
         <v>0.41</v>
       </c>
-      <c r="Q7" s="7">
-        <v>399</v>
+      <c r="Q7" s="12">
+        <v>1050</v>
       </c>
       <c r="R7" s="8">
         <v>229000000</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>39</v>
       </c>
@@ -1069,14 +1072,14 @@
       <c r="P8" s="15">
         <v>0.36</v>
       </c>
-      <c r="Q8" s="7">
-        <v>316</v>
+      <c r="Q8" s="12">
+        <v>1050</v>
       </c>
       <c r="R8" s="8">
         <v>364000000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -1125,14 +1128,14 @@
       <c r="P9" s="15">
         <v>0.35</v>
       </c>
-      <c r="Q9" s="7">
-        <v>632</v>
+      <c r="Q9" s="12">
+        <v>1040</v>
       </c>
       <c r="R9" s="8">
         <v>407000000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>41</v>
       </c>
@@ -1181,14 +1184,14 @@
       <c r="P10" s="15">
         <v>0.64</v>
       </c>
-      <c r="Q10" s="7">
-        <v>700</v>
+      <c r="Q10" s="12">
+        <v>1000</v>
       </c>
       <c r="R10" s="8">
         <v>485000000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>42</v>
       </c>
@@ -1237,14 +1240,14 @@
       <c r="P11" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q11" s="7">
-        <v>330</v>
+      <c r="Q11" s="12">
+        <v>1200</v>
       </c>
       <c r="R11" s="8">
         <v>245000000</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -1293,27 +1296,21 @@
       <c r="P12" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q12" s="7">
-        <v>330</v>
+      <c r="Q12" s="12">
+        <v>1200</v>
       </c>
       <c r="R12" s="8">
         <v>245000000</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>48</v>
-      </c>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="13"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1334,12 +1331,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC80EBF-8B96-4896-8C13-AD8A976D05A3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1367,7 +1364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1381,7 +1378,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1395,7 +1392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>

--- a/DataVaryingTemperature/LSR_20251119_all_materials.xlsx
+++ b/DataVaryingTemperature/LSR_20251119_all_materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E927CEA-6288-47CD-BB79-9833F4DCF5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691DB21F-D881-41DC-BEE0-31CD212E62C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="0" windowWidth="22164" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -322,6 +322,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,7 +754,8 @@
         <v>3201691.1808246872</v>
       </c>
       <c r="G3" s="12">
-        <v>1.0001904096107801</v>
+        <f>0.1*F3</f>
+        <v>320169.11808246875</v>
       </c>
       <c r="H3" s="12">
         <v>168216570.304768</v>
@@ -765,7 +769,8 @@
         <v>17011.179065454031</v>
       </c>
       <c r="K3" s="17">
-        <v>1.0002813979562399</v>
+        <f>0.1*J3</f>
+        <v>1701.1179065454032</v>
       </c>
       <c r="L3" s="8">
         <v>161</v>
@@ -782,7 +787,7 @@
       <c r="P3" s="15">
         <v>0.25</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="18">
         <v>435</v>
       </c>
       <c r="R3" s="8">
@@ -803,29 +808,31 @@
         <v>88122361302.941193</v>
       </c>
       <c r="E4" s="12">
-        <f t="shared" ref="E4:E5" si="0">D4*EXP(-2000/Q4)</f>
+        <f t="shared" ref="E4:E12" si="0">D4*EXP(-2000/Q4)</f>
         <v>425450353.708947</v>
       </c>
       <c r="F4" s="12">
-        <f t="shared" ref="F4:F5" si="1">0.1*D4*EXP(-3000/Q4)</f>
+        <f t="shared" ref="F4:F12" si="1">0.1*D4*EXP(-3000/Q4)</f>
         <v>2956175.8899659268</v>
       </c>
       <c r="G4" s="12">
-        <v>0.99968676964325098</v>
+        <f t="shared" ref="G4:G12" si="2">0.1*F4</f>
+        <v>295617.58899659268</v>
       </c>
       <c r="H4" s="12">
         <v>331895501.95574099</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" ref="I4:I5" si="2">0.1*H4*EXP(-2000/Q4)</f>
+        <f t="shared" ref="I4:I12" si="3">0.1*H4*EXP(-2000/Q4)</f>
         <v>160237.4886619903</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" ref="J4:J5" si="3">0.1*H4*EXP(-3000/Q4)</f>
+        <f t="shared" ref="J4:J12" si="4">0.1*H4*EXP(-3000/Q4)</f>
         <v>11133.853727509615</v>
       </c>
-      <c r="K4" s="12">
-        <v>1.00011111067342</v>
+      <c r="K4" s="17">
+        <f t="shared" ref="K4:K12" si="5">0.1*J4</f>
+        <v>1113.3853727509616</v>
       </c>
       <c r="L4" s="8">
         <v>121</v>
@@ -842,7 +849,7 @@
       <c r="P4" s="15">
         <v>0.74</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="18">
         <v>375</v>
       </c>
       <c r="R4" s="8">
@@ -871,21 +878,23 @@
         <v>1761371.0038603023</v>
       </c>
       <c r="G5" s="12">
-        <v>0.99992423656867901</v>
+        <f t="shared" si="2"/>
+        <v>176137.10038603024</v>
       </c>
       <c r="H5" s="12">
         <v>413532439.30818099</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>136403.9131325568</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7834.0340095552874</v>
       </c>
-      <c r="K5" s="12">
-        <v>1.0004243155682</v>
+      <c r="K5" s="17">
+        <f t="shared" si="5"/>
+        <v>783.40340095552881</v>
       </c>
       <c r="L5" s="8">
         <v>155</v>
@@ -902,7 +911,7 @@
       <c r="P5" s="15">
         <v>0.15</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="18">
         <v>350</v>
       </c>
       <c r="R5" s="8">
@@ -923,25 +932,31 @@
         <v>54070808940.932602</v>
       </c>
       <c r="E6" s="12">
-        <v>53063644666.036102</v>
+        <f t="shared" si="0"/>
+        <v>8048876846.430934</v>
       </c>
       <c r="F6" s="12">
-        <v>171529075344.30801</v>
+        <f t="shared" si="1"/>
+        <v>310542818.33966625</v>
       </c>
       <c r="G6" s="12">
-        <v>1.0006921851331401</v>
+        <f t="shared" si="2"/>
+        <v>31054281.833966628</v>
       </c>
       <c r="H6" s="12">
         <v>384064916.71307498</v>
       </c>
       <c r="I6" s="12">
-        <v>67336407.728308499</v>
+        <f t="shared" si="3"/>
+        <v>5717116.640580033</v>
       </c>
       <c r="J6" s="12">
-        <v>9802478271.9358501</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0.99970767300819297</v>
+        <f t="shared" si="4"/>
+        <v>2205785.4135631202</v>
+      </c>
+      <c r="K6" s="17">
+        <f t="shared" si="5"/>
+        <v>220578.54135631202</v>
       </c>
       <c r="L6" s="8">
         <v>15</v>
@@ -958,7 +973,7 @@
       <c r="P6" s="15">
         <v>0.46</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="18">
         <v>1050</v>
       </c>
       <c r="R6" s="8">
@@ -981,25 +996,31 @@
         <v>208286523523.36401</v>
       </c>
       <c r="E7" s="12">
-        <v>41621688705.959396</v>
+        <f t="shared" si="0"/>
+        <v>31005132148.886272</v>
       </c>
       <c r="F7" s="12">
-        <v>11119522273946.4</v>
+        <f t="shared" si="1"/>
+        <v>1196244060.4092991</v>
       </c>
       <c r="G7" s="12">
-        <v>1.0003021190852499</v>
+        <f t="shared" si="2"/>
+        <v>119624406.04092991</v>
       </c>
       <c r="H7" s="12">
         <v>1076144940.77356</v>
       </c>
       <c r="I7" s="12">
-        <v>140180142.13102299</v>
+        <f t="shared" si="3"/>
+        <v>16019287.054976879</v>
       </c>
       <c r="J7" s="12">
-        <v>694123231212.5</v>
-      </c>
-      <c r="K7" s="12">
-        <v>0.99944668568157702</v>
+        <f t="shared" si="4"/>
+        <v>6180582.2660220498</v>
+      </c>
+      <c r="K7" s="17">
+        <f t="shared" si="5"/>
+        <v>618058.22660220496</v>
       </c>
       <c r="L7" s="8">
         <v>15</v>
@@ -1016,7 +1037,7 @@
       <c r="P7" s="15">
         <v>0.41</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="18">
         <v>1050</v>
       </c>
       <c r="R7" s="8">
@@ -1037,25 +1058,31 @@
         <v>209574029756.772</v>
       </c>
       <c r="E8" s="12">
-        <v>51877493376.366203</v>
+        <f t="shared" si="0"/>
+        <v>31196787855.813713</v>
       </c>
       <c r="F8" s="12">
-        <v>19958155949305.102</v>
+        <f t="shared" si="1"/>
+        <v>1203638545.9400995</v>
       </c>
       <c r="G8" s="12">
-        <v>1.0003120524356199</v>
+        <f t="shared" si="2"/>
+        <v>120363854.59400995</v>
       </c>
       <c r="H8" s="12">
         <v>1122217185.4625299</v>
       </c>
       <c r="I8" s="12">
-        <v>183491963.934403</v>
+        <f t="shared" si="3"/>
+        <v>16705109.647247039</v>
       </c>
       <c r="J8" s="12">
-        <v>285480605375.97302</v>
-      </c>
-      <c r="K8" s="12">
-        <v>0.99998084198200499</v>
+        <f t="shared" si="4"/>
+        <v>6445187.2348246612</v>
+      </c>
+      <c r="K8" s="17">
+        <f t="shared" si="5"/>
+        <v>644518.72348246619</v>
       </c>
       <c r="L8" s="8">
         <v>18</v>
@@ -1072,7 +1099,7 @@
       <c r="P8" s="15">
         <v>0.36</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="18">
         <v>1050</v>
       </c>
       <c r="R8" s="8">
@@ -1093,25 +1120,31 @@
         <v>199715213010.06699</v>
       </c>
       <c r="E9" s="12">
-        <v>50388707522.034698</v>
+        <f t="shared" si="0"/>
+        <v>29189687928.361118</v>
       </c>
       <c r="F9" s="12">
-        <v>5005582473593.5303</v>
+        <f t="shared" si="1"/>
+        <v>1115934241.9398842</v>
       </c>
       <c r="G9" s="12">
-        <v>1.00279637203968</v>
+        <f t="shared" si="2"/>
+        <v>111593424.19398843</v>
       </c>
       <c r="H9" s="12">
         <v>367949011.25479698</v>
       </c>
       <c r="I9" s="12">
-        <v>81602444.260290399</v>
+        <f t="shared" si="3"/>
+        <v>5377816.0662879366</v>
       </c>
       <c r="J9" s="12">
-        <v>19124155940.442501</v>
-      </c>
-      <c r="K9" s="12">
-        <v>0.99981116858122199</v>
+        <f t="shared" si="4"/>
+        <v>2055962.060969559</v>
+      </c>
+      <c r="K9" s="17">
+        <f t="shared" si="5"/>
+        <v>205596.20609695592</v>
       </c>
       <c r="L9" s="8">
         <v>13</v>
@@ -1128,7 +1161,7 @@
       <c r="P9" s="15">
         <v>0.35</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="18">
         <v>1040</v>
       </c>
       <c r="R9" s="8">
@@ -1149,25 +1182,31 @@
         <v>279194502269.96802</v>
       </c>
       <c r="E10" s="12">
-        <v>112080318552.16499</v>
+        <f t="shared" si="0"/>
+        <v>37784867042.811234</v>
       </c>
       <c r="F10" s="12">
-        <v>3667722145062.27</v>
+        <f t="shared" si="1"/>
+        <v>1390027577.2446644</v>
       </c>
       <c r="G10" s="12">
-        <v>1.00055405463834</v>
+        <f t="shared" si="2"/>
+        <v>139002757.72446644</v>
       </c>
       <c r="H10" s="12">
         <v>1223876264.4957099</v>
       </c>
       <c r="I10" s="12">
-        <v>692345364.51628304</v>
+        <f t="shared" si="3"/>
+        <v>16563364.090209443</v>
       </c>
       <c r="J10" s="12">
-        <v>26710952266.052299</v>
-      </c>
-      <c r="K10" s="12">
-        <v>1.0003928619167901</v>
+        <f t="shared" si="4"/>
+        <v>6093321.1254253853</v>
+      </c>
+      <c r="K10" s="17">
+        <f t="shared" si="5"/>
+        <v>609332.11254253855</v>
       </c>
       <c r="L10" s="8">
         <v>10</v>
@@ -1184,7 +1223,7 @@
       <c r="P10" s="15">
         <v>0.64</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="18">
         <v>1000</v>
       </c>
       <c r="R10" s="8">
@@ -1205,25 +1244,31 @@
         <v>117108650073.651</v>
       </c>
       <c r="E11" s="12">
-        <v>44884386172.699799</v>
+        <f t="shared" si="0"/>
+        <v>22118966880.153912</v>
       </c>
       <c r="F11" s="12">
-        <v>175213569928.29001</v>
+        <f t="shared" si="1"/>
+        <v>961286338.01422894</v>
       </c>
       <c r="G11" s="12">
-        <v>1.0007894571356</v>
+        <f t="shared" si="2"/>
+        <v>96128633.801422894</v>
       </c>
       <c r="H11" s="12">
         <v>425435242.49228698</v>
       </c>
       <c r="I11" s="12">
-        <v>77030174.758169293</v>
+        <f t="shared" si="3"/>
+        <v>8035433.789407501</v>
       </c>
       <c r="J11" s="12">
-        <v>751102621.40532196</v>
-      </c>
-      <c r="K11" s="12">
-        <v>0.99976714584067305</v>
+        <f t="shared" si="4"/>
+        <v>3492185.1294537433</v>
+      </c>
+      <c r="K11" s="17">
+        <f t="shared" si="5"/>
+        <v>349218.51294537436</v>
       </c>
       <c r="L11" s="8">
         <v>17</v>
@@ -1240,7 +1285,7 @@
       <c r="P11" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="18">
         <v>1200</v>
       </c>
       <c r="R11" s="8">
@@ -1261,25 +1306,31 @@
         <v>137833413174.57401</v>
       </c>
       <c r="E12" s="12">
-        <v>26190448754.770599</v>
+        <f t="shared" si="0"/>
+        <v>26033369004.506401</v>
       </c>
       <c r="F12" s="12">
-        <v>13930248415001.699</v>
+        <f t="shared" si="1"/>
+        <v>1131405553.0762184</v>
       </c>
       <c r="G12" s="12">
-        <v>1.0010307445001101</v>
+        <f t="shared" si="2"/>
+        <v>113140555.30762184</v>
       </c>
       <c r="H12" s="12">
         <v>504059502.99034601</v>
       </c>
       <c r="I12" s="12">
-        <v>68511256.134603202</v>
+        <f t="shared" si="3"/>
+        <v>9520454.24933034</v>
       </c>
       <c r="J12" s="12">
-        <v>8072139562.2192097</v>
-      </c>
-      <c r="K12" s="12">
-        <v>1.0002667881887199</v>
+        <f t="shared" si="4"/>
+        <v>4137572.3609325667</v>
+      </c>
+      <c r="K12" s="17">
+        <f t="shared" si="5"/>
+        <v>413757.23609325668</v>
       </c>
       <c r="L12" s="8">
         <v>17</v>
@@ -1296,7 +1347,7 @@
       <c r="P12" s="15">
         <v>1E-3</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="18">
         <v>1200</v>
       </c>
       <c r="R12" s="8">
